--- a/PHY-4B/labs/lab4/Delano Leslie - Lab 4 - Parallel Plate Capacitor.xlsx
+++ b/PHY-4B/labs/lab4/Delano Leslie - Lab 4 - Parallel Plate Capacitor.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Lab 4 - White Paper" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="41">
   <si>
     <t xml:space="preserve">Name:</t>
   </si>
@@ -82,6 +82,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Part 1: vary </t>
     </r>
@@ -93,6 +94,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">d</t>
     </r>
@@ -103,6 +105,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> while holding </t>
     </r>
@@ -114,6 +117,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">A</t>
     </r>
@@ -124,6 +128,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> constant</t>
     </r>
@@ -160,6 +165,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">0</t>
     </r>
@@ -170,6 +176,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> w L</t>
     </r>
@@ -182,6 +189,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Part 2: vary </t>
     </r>
@@ -193,6 +201,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">A</t>
     </r>
@@ -203,6 +212,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> while holding </t>
     </r>
@@ -214,6 +224,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">d</t>
     </r>
@@ -224,6 +235,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> constant</t>
     </r>
@@ -251,6 +263,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">0</t>
     </r>
@@ -261,6 +274,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> w</t>
     </r>
@@ -284,6 +298,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">d</t>
     </r>
@@ -294,6 +309,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-1</t>
     </r>
@@ -303,6 +319,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">(m</t>
     </r>
@@ -313,6 +330,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-1</t>
     </r>
@@ -322,6 +340,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
@@ -330,34 +349,270 @@
     <t xml:space="preserve">C(pF)</t>
   </si>
   <si>
-    <t xml:space="preserve">b(m)</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8.854187817 × 10</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/N.m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)(0.255 m)(0.102 m)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">b(mm)</t>
   </si>
   <si>
     <t xml:space="preserve">x(m)</t>
   </si>
   <si>
+    <t xml:space="preserve">(0.37 mm)(127688.651)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8.854187817 × 10-12 C2/N.m2)(0.255 m)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dielectric Data - Waxed Paper</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8.854x10</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/N.m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) (0.102 m) (0.255 m)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">b(m)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8.854x10</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/N.m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) (0.102 m)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.00%"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="171" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -380,6 +635,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -387,6 +643,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -395,6 +652,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -402,6 +660,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -410,6 +669,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -418,12 +678,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -439,6 +701,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -455,6 +718,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -462,6 +726,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -475,6 +740,23 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -595,201 +877,217 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -869,7 +1167,53 @@
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Area Effect on Capacitance
+</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1100" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>x(m) v.s. C(pF)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
@@ -926,12 +1270,17 @@
                 <a:p>
                   <a:pPr>
                     <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
                       <a:uFillTx/>
                       <a:latin typeface="Arial"/>
+                      <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
               </c:txPr>
+              <c:dLblPos val="r"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -945,12 +1294,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -992,34 +1346,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.02</c:v>
+                  <c:v>0.235</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.03</c:v>
+                  <c:v>0.225</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.04</c:v>
+                  <c:v>0.215</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.05</c:v>
+                  <c:v>0.205</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.06</c:v>
+                  <c:v>0.195</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.07</c:v>
+                  <c:v>0.185</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.08</c:v>
+                  <c:v>0.175</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.09</c:v>
+                  <c:v>0.165</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1</c:v>
+                  <c:v>0.155</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.11</c:v>
+                  <c:v>0.145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1065,17 +1419,47 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="74975763"/>
-        <c:axId val="98143669"/>
+        <c:axId val="82894738"/>
+        <c:axId val="94048424"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="74975763"/>
+        <c:axId val="82894738"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>x(m)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1092,18 +1476,22 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98143669"/>
+        <c:crossAx val="94048424"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="98143669"/>
+        <c:axId val="94048424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1118,7 +1506,37 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>C(pF)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1135,15 +1553,19 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74975763"/>
+        <c:crossAx val="82894738"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1154,28 +1576,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="span"/>
   </c:chart>
@@ -1195,7 +1595,53 @@
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Dielectric Seperation Effect on Capacitance
+</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1100" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>d^-1(m^-1) v.s. C(pF)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
@@ -1238,12 +1684,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1358,17 +1809,47 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="70117979"/>
-        <c:axId val="39292847"/>
+        <c:axId val="99688166"/>
+        <c:axId val="34706090"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="70117979"/>
+        <c:axId val="99688166"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>d^-1(m^-1)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1385,18 +1866,22 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39292847"/>
+        <c:crossAx val="34706090"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="39292847"/>
+        <c:axId val="34706090"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1411,7 +1896,37 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>d^-1(m^-1)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1428,15 +1943,19 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70117979"/>
+        <c:crossAx val="99688166"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1447,28 +1966,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="span"/>
   </c:chart>
@@ -1488,7 +1985,53 @@
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Dielectric Seperation Effect on Capacitance
+</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1100" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>d^-1(m^-1) v.s. C(pF)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
@@ -1531,12 +2074,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1575,7 +2123,7 @@
             <c:numRef>
               <c:f>'Lab 4 - Waxed Paper'!$G$25:$G$32</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>42424.2424242424</c:v>
@@ -1639,17 +2187,47 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="15823861"/>
-        <c:axId val="74811420"/>
+        <c:axId val="38579043"/>
+        <c:axId val="86737948"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="15823861"/>
+        <c:axId val="38579043"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>d^-1(m^-1)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1666,18 +2244,22 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74811420"/>
+        <c:crossAx val="86737948"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="74811420"/>
+        <c:axId val="86737948"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1692,7 +2274,37 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>C(pF)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1709,15 +2321,19 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15823861"/>
+        <c:crossAx val="38579043"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1728,28 +2344,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="span"/>
   </c:chart>
@@ -1769,7 +2363,53 @@
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Area Effect On Capacitance
+</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1100" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>x(m) v.s. C(pF)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
@@ -1805,19 +2445,61 @@
               </a:solidFill>
             </c:spPr>
           </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="square"/>
+              <c:size val="8"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="004586"/>
+                </a:solidFill>
+              </c:spPr>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:uFillTx/>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1838,6 +2520,34 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="0">
+                <a:solidFill>
+                  <a:srgbClr val="004586"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="0"/>
+            <c:backward val="0"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="0">
+                <a:solidFill>
+                  <a:srgbClr val="004586"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="0"/>
+            <c:backward val="0"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'Lab 4 - Waxed Paper'!$G$41:$G$50</c:f>
@@ -1845,22 +2555,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.02</c:v>
+                  <c:v>0.235</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.03</c:v>
+                  <c:v>0.225</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.04</c:v>
+                  <c:v>0.215</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.05</c:v>
+                  <c:v>0.205</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.06</c:v>
+                  <c:v>0.195</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.07</c:v>
+                  <c:v>0.185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1894,17 +2604,47 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="21404177"/>
-        <c:axId val="78795388"/>
+        <c:axId val="21462536"/>
+        <c:axId val="54741897"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="21404177"/>
+        <c:axId val="21462536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>x(m)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1921,18 +2661,22 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78795388"/>
+        <c:crossAx val="54741897"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="78795388"/>
+        <c:axId val="54741897"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1947,7 +2691,37 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>C(pF)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1964,15 +2738,19 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21404177"/>
+        <c:crossAx val="21462536"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1983,28 +2761,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="span"/>
   </c:chart>
@@ -2023,16 +2779,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>86040</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>201960</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>284400</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>1440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>560520</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>88920</xdr:rowOff>
+      <xdr:colOff>146880</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>50040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2040,8 +2796,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5056200" y="10723320"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="4642920" y="10136160"/>
+        <a:ext cx="5759280" cy="3239280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2054,15 +2810,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>398520</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>274320</xdr:rowOff>
+      <xdr:colOff>277920</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>76680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>259920</xdr:colOff>
+      <xdr:colOff>183600</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>160200</xdr:rowOff>
+      <xdr:rowOff>113040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2070,8 +2826,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4757040" y="5962680"/>
-        <a:ext cx="5758200" cy="3238560"/>
+        <a:off x="4636440" y="5362920"/>
+        <a:ext cx="5802480" cy="3836880"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2088,16 +2844,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>236520</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>150480</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>45000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>157680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>431280</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>497520</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>156240</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2105,8 +2861,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4343760" y="5838840"/>
-        <a:ext cx="5758560" cy="3238560"/>
+        <a:off x="4403520" y="4901040"/>
+        <a:ext cx="6349320" cy="4089960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2119,15 +2875,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>132120</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>258840</xdr:rowOff>
+      <xdr:colOff>248400</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>126000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>579240</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>145800</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>110880</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>240840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2135,8 +2891,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4490640" y="10170720"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="4606920" y="9108000"/>
+        <a:ext cx="5759280" cy="3239280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2263,854 +3019,854 @@
   <dimension ref="B1:AD54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="13" style="0" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="2.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="7.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="2.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="13" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="2.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="7.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="2.29"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8" t="s">
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14"/>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="14"/>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <f aca="false">25.5/100</f>
         <v>0.255</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19" t="n">
+      <c r="F8" s="20"/>
+      <c r="G8" s="20" t="n">
         <v>0.225</v>
       </c>
-      <c r="H8" s="16"/>
+      <c r="H8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="14"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">10.2/100</f>
         <v>0.102</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19" t="n">
+      <c r="F9" s="20"/>
+      <c r="G9" s="20" t="n">
         <v>0.101</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="23"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="19"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="14"/>
-      <c r="C13" s="24" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="19"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="14"/>
-      <c r="C14" s="25" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18" t="n">
+      <c r="D14" s="26"/>
+      <c r="E14" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="F14" s="26"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="19"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="14"/>
-      <c r="C15" s="25" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18" t="n">
+      <c r="D15" s="26"/>
+      <c r="E15" s="19" t="n">
         <v>2.08</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="19"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="14"/>
-      <c r="C16" s="25" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="26" t="s">
+      <c r="D16" s="26"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="19"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" customFormat="false" ht="8.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="13"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
-      <c r="AA21" s="12"/>
-      <c r="AB21" s="12"/>
-      <c r="AC21" s="12"/>
-      <c r="AD21" s="13"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="14"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="16"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="30" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="17"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="19"/>
-      <c r="AB22" s="19"/>
-      <c r="AC22" s="19"/>
-      <c r="AD22" s="16"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="16"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="19"/>
-      <c r="AB23" s="19"/>
-      <c r="AC23" s="19"/>
-      <c r="AD23" s="16"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="17"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="16"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="32" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="17"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="X24" s="33"/>
-      <c r="Y24" s="33"/>
-      <c r="Z24" s="18"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="19"/>
-      <c r="AC24" s="19"/>
-      <c r="AD24" s="16"/>
+      <c r="X24" s="34"/>
+      <c r="Y24" s="34"/>
+      <c r="Z24" s="19"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AD24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="14"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="16"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="33"/>
-      <c r="Y25" s="33"/>
-      <c r="Z25" s="18"/>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="16"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="17"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="34"/>
+      <c r="X25" s="34"/>
+      <c r="Y25" s="34"/>
+      <c r="Z25" s="19"/>
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="20"/>
+      <c r="AD25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="14"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="16"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="34" t="s">
+      <c r="B26" s="15"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="17"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="X26" s="33" t="s">
+      <c r="X26" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="Y26" s="35" t="s">
+      <c r="Y26" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="Z26" s="33" t="s">
+      <c r="Z26" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AA26" s="22"/>
-      <c r="AB26" s="33" t="s">
+      <c r="AA26" s="23"/>
+      <c r="AB26" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AC26" s="36"/>
-      <c r="AD26" s="16"/>
+      <c r="AC26" s="37"/>
+      <c r="AD26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="16"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="34"/>
-      <c r="X27" s="33"/>
-      <c r="Y27" s="37" t="s">
+      <c r="B27" s="15"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="17"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="35"/>
+      <c r="X27" s="34"/>
+      <c r="Y27" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="Z27" s="33"/>
-      <c r="AA27" s="19"/>
-      <c r="AB27" s="33"/>
-      <c r="AC27" s="36"/>
-      <c r="AD27" s="16"/>
+      <c r="Z27" s="34"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="34"/>
+      <c r="AC27" s="37"/>
+      <c r="AD27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="14"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="16"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="22"/>
-      <c r="X28" s="22"/>
-      <c r="Y28" s="22"/>
-      <c r="Z28" s="22"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="22"/>
-      <c r="AC28" s="22"/>
-      <c r="AD28" s="23"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="17"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="23"/>
+      <c r="X28" s="23"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="23"/>
+      <c r="AA28" s="23"/>
+      <c r="AB28" s="23"/>
+      <c r="AC28" s="23"/>
+      <c r="AD28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="16"/>
-      <c r="V29" s="19"/>
-      <c r="W29" s="38"/>
-      <c r="X29" s="38"/>
-      <c r="Y29" s="38"/>
-      <c r="Z29" s="38"/>
-      <c r="AA29" s="38"/>
-      <c r="AB29" s="38"/>
-      <c r="AC29" s="19"/>
-      <c r="AD29" s="19"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="17"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="39"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="39"/>
+      <c r="AB29" s="39"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="14"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="16"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="39"/>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="39"/>
-      <c r="Z30" s="39"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="32"/>
-      <c r="AD30" s="19"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="17"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="40"/>
+      <c r="X30" s="40"/>
+      <c r="Y30" s="40"/>
+      <c r="Z30" s="40"/>
+      <c r="AA30" s="19"/>
+      <c r="AB30" s="19"/>
+      <c r="AC30" s="33"/>
+      <c r="AD30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="16"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="19"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="19"/>
-      <c r="Z31" s="19"/>
-      <c r="AA31" s="19"/>
-      <c r="AB31" s="19"/>
-      <c r="AC31" s="19"/>
-      <c r="AD31" s="19"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="17"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="20"/>
+      <c r="AD31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="16"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="38"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="19"/>
-      <c r="Z32" s="19"/>
-      <c r="AA32" s="19"/>
-      <c r="AB32" s="19"/>
-      <c r="AC32" s="19"/>
-      <c r="AD32" s="19"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="17"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="39"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
+      <c r="AC32" s="20"/>
+      <c r="AD32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="14"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="16"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="19"/>
-      <c r="X33" s="19"/>
-      <c r="Y33" s="19"/>
-      <c r="Z33" s="19"/>
-      <c r="AA33" s="19"/>
-      <c r="AB33" s="19"/>
-      <c r="AC33" s="19"/>
-      <c r="AD33" s="19"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="17"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="20"/>
+      <c r="AA33" s="20"/>
+      <c r="AB33" s="20"/>
+      <c r="AC33" s="20"/>
+      <c r="AD33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="14"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="16"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="40"/>
-      <c r="X34" s="41"/>
-      <c r="Y34" s="33"/>
-      <c r="Z34" s="18"/>
-      <c r="AA34" s="18"/>
-      <c r="AB34" s="19"/>
-      <c r="AC34" s="19"/>
-      <c r="AD34" s="19"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="20"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="23"/>
-      <c r="V35" s="19"/>
-      <c r="W35" s="19"/>
-      <c r="X35" s="19"/>
-      <c r="Y35" s="19"/>
-      <c r="Z35" s="19"/>
-      <c r="AA35" s="19"/>
-      <c r="AB35" s="19"/>
-      <c r="AC35" s="19"/>
-      <c r="AD35" s="19"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="17"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="41"/>
+      <c r="X34" s="42"/>
+      <c r="Y34" s="34"/>
+      <c r="Z34" s="19"/>
+      <c r="AA34" s="19"/>
+      <c r="AB34" s="20"/>
+      <c r="AC34" s="20"/>
+      <c r="AD34" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="21"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="24"/>
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+      <c r="Z35" s="20"/>
+      <c r="AA35" s="20"/>
+      <c r="AB35" s="20"/>
+      <c r="AC35" s="20"/>
+      <c r="AD35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="1"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
     </row>
     <row r="37" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D37" s="43"/>
-      <c r="E37" s="43" t="s">
+      <c r="D37" s="44"/>
+      <c r="E37" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
     </row>
     <row r="38" customFormat="false" ht="8.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D39" s="10"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="13"/>
-      <c r="V39" s="10"/>
-      <c r="W39" s="12"/>
-      <c r="X39" s="12"/>
-      <c r="Y39" s="12"/>
-      <c r="Z39" s="12"/>
-      <c r="AA39" s="12"/>
-      <c r="AB39" s="12"/>
-      <c r="AC39" s="12"/>
-      <c r="AD39" s="13"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="14"/>
+      <c r="V39" s="11"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="13"/>
+      <c r="AD39" s="14"/>
     </row>
     <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D40" s="14"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="45"/>
-      <c r="V40" s="14"/>
-      <c r="W40" s="30" t="s">
+      <c r="D40" s="15"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="46"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="19"/>
-      <c r="AB40" s="19"/>
-      <c r="AC40" s="19"/>
-      <c r="AD40" s="16"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="31"/>
+      <c r="AA40" s="20"/>
+      <c r="AB40" s="20"/>
+      <c r="AC40" s="20"/>
+      <c r="AD40" s="17"/>
     </row>
     <row r="41" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D41" s="14"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="16"/>
-      <c r="V41" s="14"/>
-      <c r="W41" s="31"/>
-      <c r="X41" s="31"/>
-      <c r="Y41" s="31"/>
-      <c r="Z41" s="31"/>
-      <c r="AA41" s="19"/>
-      <c r="AB41" s="19"/>
-      <c r="AC41" s="19"/>
-      <c r="AD41" s="16"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="17"/>
+      <c r="V41" s="15"/>
+      <c r="W41" s="32"/>
+      <c r="X41" s="32"/>
+      <c r="Y41" s="32"/>
+      <c r="Z41" s="32"/>
+      <c r="AA41" s="20"/>
+      <c r="AB41" s="20"/>
+      <c r="AC41" s="20"/>
+      <c r="AD41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D42" s="14"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="16"/>
-      <c r="V42" s="14"/>
-      <c r="W42" s="32" t="s">
+      <c r="D42" s="15"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="17"/>
+      <c r="V42" s="15"/>
+      <c r="W42" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="X42" s="33"/>
-      <c r="Y42" s="33"/>
-      <c r="Z42" s="18"/>
-      <c r="AA42" s="19"/>
-      <c r="AB42" s="19"/>
-      <c r="AC42" s="19"/>
-      <c r="AD42" s="16"/>
+      <c r="X42" s="34"/>
+      <c r="Y42" s="34"/>
+      <c r="Z42" s="19"/>
+      <c r="AA42" s="20"/>
+      <c r="AB42" s="20"/>
+      <c r="AC42" s="20"/>
+      <c r="AD42" s="17"/>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D43" s="14"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="16"/>
-      <c r="V43" s="14"/>
-      <c r="W43" s="33"/>
-      <c r="X43" s="33"/>
-      <c r="Y43" s="33"/>
-      <c r="Z43" s="18"/>
-      <c r="AA43" s="19"/>
-      <c r="AB43" s="19"/>
-      <c r="AC43" s="19"/>
-      <c r="AD43" s="16"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="17"/>
+      <c r="V43" s="15"/>
+      <c r="W43" s="34"/>
+      <c r="X43" s="34"/>
+      <c r="Y43" s="34"/>
+      <c r="Z43" s="19"/>
+      <c r="AA43" s="20"/>
+      <c r="AB43" s="20"/>
+      <c r="AC43" s="20"/>
+      <c r="AD43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D44" s="14"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="16"/>
-      <c r="V44" s="14"/>
-      <c r="W44" s="34" t="s">
+      <c r="D44" s="15"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="17"/>
+      <c r="V44" s="15"/>
+      <c r="W44" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="X44" s="33" t="s">
+      <c r="X44" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="Y44" s="35" t="s">
+      <c r="Y44" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="Z44" s="33" t="s">
+      <c r="Z44" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AA44" s="22"/>
-      <c r="AB44" s="33" t="s">
+      <c r="AA44" s="23"/>
+      <c r="AB44" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AC44" s="36"/>
-      <c r="AD44" s="16"/>
+      <c r="AC44" s="37"/>
+      <c r="AD44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D45" s="14"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="16"/>
-      <c r="V45" s="14"/>
-      <c r="W45" s="34"/>
-      <c r="X45" s="33"/>
-      <c r="Y45" s="37" t="s">
+      <c r="D45" s="15"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="17"/>
+      <c r="V45" s="15"/>
+      <c r="W45" s="35"/>
+      <c r="X45" s="34"/>
+      <c r="Y45" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="Z45" s="33"/>
-      <c r="AA45" s="19"/>
-      <c r="AB45" s="33"/>
-      <c r="AC45" s="36"/>
-      <c r="AD45" s="16"/>
+      <c r="Z45" s="34"/>
+      <c r="AA45" s="20"/>
+      <c r="AB45" s="34"/>
+      <c r="AC45" s="37"/>
+      <c r="AD45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D46" s="14"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="16"/>
-      <c r="V46" s="20"/>
-      <c r="W46" s="22"/>
-      <c r="X46" s="22"/>
-      <c r="Y46" s="22"/>
-      <c r="Z46" s="22"/>
-      <c r="AA46" s="22"/>
-      <c r="AB46" s="22"/>
-      <c r="AC46" s="22"/>
-      <c r="AD46" s="23"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="17"/>
+      <c r="V46" s="21"/>
+      <c r="W46" s="23"/>
+      <c r="X46" s="23"/>
+      <c r="Y46" s="23"/>
+      <c r="Z46" s="23"/>
+      <c r="AA46" s="23"/>
+      <c r="AB46" s="23"/>
+      <c r="AC46" s="23"/>
+      <c r="AD46" s="24"/>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D47" s="14"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="16"/>
-      <c r="V47" s="19"/>
-      <c r="W47" s="38"/>
-      <c r="X47" s="38"/>
-      <c r="Y47" s="38"/>
-      <c r="Z47" s="38"/>
-      <c r="AA47" s="38"/>
-      <c r="AB47" s="38"/>
-      <c r="AC47" s="19"/>
-      <c r="AD47" s="19"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="17"/>
+      <c r="V47" s="20"/>
+      <c r="W47" s="39"/>
+      <c r="X47" s="39"/>
+      <c r="Y47" s="39"/>
+      <c r="Z47" s="39"/>
+      <c r="AA47" s="39"/>
+      <c r="AB47" s="39"/>
+      <c r="AC47" s="20"/>
+      <c r="AD47" s="20"/>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D48" s="14"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="16"/>
-      <c r="V48" s="19"/>
-      <c r="W48" s="39"/>
-      <c r="X48" s="39"/>
-      <c r="Y48" s="39"/>
-      <c r="Z48" s="39"/>
-      <c r="AA48" s="18"/>
-      <c r="AB48" s="18"/>
-      <c r="AC48" s="32"/>
-      <c r="AD48" s="19"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="17"/>
+      <c r="V48" s="20"/>
+      <c r="W48" s="40"/>
+      <c r="X48" s="40"/>
+      <c r="Y48" s="40"/>
+      <c r="Z48" s="40"/>
+      <c r="AA48" s="19"/>
+      <c r="AB48" s="19"/>
+      <c r="AC48" s="33"/>
+      <c r="AD48" s="20"/>
     </row>
     <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D49" s="14"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="16"/>
-      <c r="V49" s="19"/>
-      <c r="W49" s="19"/>
-      <c r="X49" s="19"/>
-      <c r="Y49" s="19"/>
-      <c r="Z49" s="19"/>
-      <c r="AA49" s="19"/>
-      <c r="AB49" s="19"/>
-      <c r="AC49" s="19"/>
-      <c r="AD49" s="19"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="17"/>
+      <c r="V49" s="20"/>
+      <c r="W49" s="20"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
+      <c r="Z49" s="20"/>
+      <c r="AA49" s="20"/>
+      <c r="AB49" s="20"/>
+      <c r="AC49" s="20"/>
+      <c r="AD49" s="20"/>
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D50" s="14"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="16"/>
-      <c r="V50" s="19"/>
-      <c r="W50" s="38"/>
-      <c r="X50" s="19"/>
-      <c r="Y50" s="19"/>
-      <c r="Z50" s="19"/>
-      <c r="AA50" s="19"/>
-      <c r="AB50" s="19"/>
-      <c r="AC50" s="19"/>
-      <c r="AD50" s="19"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="17"/>
+      <c r="V50" s="20"/>
+      <c r="W50" s="39"/>
+      <c r="X50" s="20"/>
+      <c r="Y50" s="20"/>
+      <c r="Z50" s="20"/>
+      <c r="AA50" s="20"/>
+      <c r="AB50" s="20"/>
+      <c r="AC50" s="20"/>
+      <c r="AD50" s="20"/>
     </row>
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D51" s="14"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="16"/>
-      <c r="V51" s="19"/>
-      <c r="W51" s="19"/>
-      <c r="X51" s="19"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="19"/>
-      <c r="AA51" s="19"/>
-      <c r="AB51" s="19"/>
-      <c r="AC51" s="19"/>
-      <c r="AD51" s="19"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="17"/>
+      <c r="V51" s="20"/>
+      <c r="W51" s="20"/>
+      <c r="X51" s="20"/>
+      <c r="Y51" s="20"/>
+      <c r="Z51" s="20"/>
+      <c r="AA51" s="20"/>
+      <c r="AB51" s="20"/>
+      <c r="AC51" s="20"/>
+      <c r="AD51" s="20"/>
     </row>
     <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D52" s="14"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="16"/>
-      <c r="V52" s="19"/>
-      <c r="W52" s="40"/>
-      <c r="X52" s="41"/>
-      <c r="Y52" s="33"/>
-      <c r="Z52" s="18"/>
-      <c r="AA52" s="18"/>
-      <c r="AB52" s="19"/>
-      <c r="AC52" s="19"/>
-      <c r="AD52" s="19"/>
-    </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D53" s="20"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="23"/>
-      <c r="V53" s="19"/>
-      <c r="W53" s="19"/>
-      <c r="X53" s="19"/>
-      <c r="Y53" s="19"/>
-      <c r="Z53" s="19"/>
-      <c r="AA53" s="19"/>
-      <c r="AB53" s="19"/>
-      <c r="AC53" s="19"/>
-      <c r="AD53" s="19"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="17"/>
+      <c r="V52" s="20"/>
+      <c r="W52" s="41"/>
+      <c r="X52" s="42"/>
+      <c r="Y52" s="34"/>
+      <c r="Z52" s="19"/>
+      <c r="AA52" s="19"/>
+      <c r="AB52" s="20"/>
+      <c r="AC52" s="20"/>
+      <c r="AD52" s="20"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D53" s="21"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="23"/>
+      <c r="I53" s="23"/>
+      <c r="J53" s="24"/>
+      <c r="V53" s="20"/>
+      <c r="W53" s="20"/>
+      <c r="X53" s="20"/>
+      <c r="Y53" s="20"/>
+      <c r="Z53" s="20"/>
+      <c r="AA53" s="20"/>
+      <c r="AB53" s="20"/>
+      <c r="AC53" s="20"/>
+      <c r="AD53" s="20"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="1"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -3158,1063 +3914,1088 @@
   <dimension ref="B1:AD54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="13" style="0" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="2.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="7.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="2.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="13" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="2.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="7.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="2.29"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14"/>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="14"/>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <f aca="false">25.5/100</f>
         <v>0.255</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19" t="n">
+      <c r="F8" s="20"/>
+      <c r="G8" s="20" t="n">
         <v>0.255</v>
       </c>
-      <c r="H8" s="16"/>
+      <c r="H8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="14"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">10.2/100</f>
         <v>0.102</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19" t="n">
+      <c r="F9" s="20"/>
+      <c r="G9" s="20" t="n">
         <v>0.101</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="23"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="19"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="14"/>
-      <c r="C13" s="24" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="19"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="14"/>
-      <c r="C14" s="25" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18" t="n">
+      <c r="D14" s="26"/>
+      <c r="E14" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="F14" s="26"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="19"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="14"/>
-      <c r="C15" s="25" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="46" t="n">
+      <c r="D15" s="26"/>
+      <c r="E15" s="47" t="n">
         <v>3.7</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="19"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="14"/>
-      <c r="C16" s="25" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18" t="n">
+      <c r="D16" s="26"/>
+      <c r="E16" s="19" t="n">
         <f aca="false">E15/E14</f>
         <v>0.185</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="19"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" customFormat="false" ht="8.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="13"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
-      <c r="AA21" s="12"/>
-      <c r="AB21" s="12"/>
-      <c r="AC21" s="12"/>
-      <c r="AD21" s="13"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="14"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14"/>
-      <c r="C22" s="29" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="16"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="30" t="s">
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="17"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="19"/>
-      <c r="AB22" s="19"/>
-      <c r="AC22" s="19"/>
-      <c r="AD22" s="16"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="16"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="19"/>
-      <c r="AB23" s="19"/>
-      <c r="AC23" s="19"/>
-      <c r="AD23" s="16"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="17"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14"/>
-      <c r="C24" s="21" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="21" t="s">
+      <c r="D24" s="19"/>
+      <c r="E24" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="22" t="s">
+      <c r="F24" s="20"/>
+      <c r="G24" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="H24" s="19"/>
-      <c r="I24" s="22" t="s">
+      <c r="H24" s="20"/>
+      <c r="I24" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="16"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="32" t="s">
+      <c r="J24" s="17"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="X24" s="33"/>
-      <c r="Y24" s="33"/>
-      <c r="Z24" s="18"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="19"/>
-      <c r="AC24" s="19"/>
-      <c r="AD24" s="16"/>
+      <c r="X24" s="34"/>
+      <c r="Y24" s="34"/>
+      <c r="Z24" s="19"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AD24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="14"/>
-      <c r="C25" s="18" t="n">
+      <c r="B25" s="15"/>
+      <c r="C25" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18" t="n">
+      <c r="D25" s="19"/>
+      <c r="E25" s="19" t="n">
         <f aca="false">C25*$E$16</f>
         <v>0.185</v>
       </c>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19" t="n">
+      <c r="F25" s="20"/>
+      <c r="G25" s="20" t="n">
         <f aca="false">1000/E25</f>
         <v>5405.40540540541</v>
       </c>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19" t="n">
+      <c r="H25" s="20"/>
+      <c r="I25" s="20" t="n">
         <v>1868</v>
       </c>
-      <c r="J25" s="16"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="33"/>
-      <c r="Y25" s="33"/>
-      <c r="Z25" s="18"/>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="16"/>
+      <c r="J25" s="17"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="34"/>
+      <c r="X25" s="34"/>
+      <c r="Y25" s="34"/>
+      <c r="Z25" s="19"/>
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="20"/>
+      <c r="AD25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="14"/>
-      <c r="C26" s="18" t="n">
+      <c r="B26" s="15"/>
+      <c r="C26" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18" t="n">
+      <c r="D26" s="19"/>
+      <c r="E26" s="19" t="n">
         <f aca="false">C26*$E$16</f>
         <v>0.37</v>
       </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19" t="n">
+      <c r="F26" s="20"/>
+      <c r="G26" s="20" t="n">
         <f aca="false">1000/E26</f>
         <v>2702.7027027027</v>
       </c>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19" t="n">
+      <c r="H26" s="20"/>
+      <c r="I26" s="20" t="n">
         <f aca="false">1.23*1000</f>
         <v>1230</v>
       </c>
-      <c r="J26" s="16"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="34" t="s">
+      <c r="J26" s="17"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="X26" s="33" t="s">
+      <c r="X26" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="Y26" s="35" t="s">
+      <c r="Y26" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="Z26" s="33" t="s">
+      <c r="Z26" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AA26" s="22"/>
-      <c r="AB26" s="33" t="s">
+      <c r="AA26" s="23" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AB26" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AC26" s="36"/>
-      <c r="AD26" s="16"/>
+      <c r="AC26" s="37" t="n">
+        <f aca="false">0.333/(8.854 * 0.255 * 0.102)</f>
+        <v>1.44598691733566</v>
+      </c>
+      <c r="AD26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14"/>
-      <c r="C27" s="18" t="n">
+      <c r="B27" s="15"/>
+      <c r="C27" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18" t="n">
+      <c r="D27" s="19"/>
+      <c r="E27" s="19" t="n">
         <f aca="false">C27*$E$16</f>
         <v>0.555</v>
       </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19" t="n">
+      <c r="F27" s="20"/>
+      <c r="G27" s="20" t="n">
         <f aca="false">1000/E27</f>
         <v>1801.8018018018</v>
       </c>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19" t="n">
+      <c r="H27" s="20"/>
+      <c r="I27" s="20" t="n">
         <f aca="false">0.81*1000</f>
         <v>810</v>
       </c>
-      <c r="J27" s="16"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="34"/>
-      <c r="X27" s="33"/>
-      <c r="Y27" s="37" t="s">
+      <c r="J27" s="17"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="35"/>
+      <c r="X27" s="34"/>
+      <c r="Y27" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="Z27" s="33"/>
-      <c r="AA27" s="19"/>
-      <c r="AB27" s="33"/>
-      <c r="AC27" s="36"/>
-      <c r="AD27" s="16"/>
+      <c r="Z27" s="34"/>
+      <c r="AA27" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB27" s="34"/>
+      <c r="AC27" s="37"/>
+      <c r="AD27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="14"/>
-      <c r="C28" s="18" t="n">
+      <c r="B28" s="15"/>
+      <c r="C28" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18" t="n">
+      <c r="D28" s="19"/>
+      <c r="E28" s="19" t="n">
         <f aca="false">C28*$E$16</f>
         <v>0.74</v>
       </c>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19" t="n">
+      <c r="F28" s="20"/>
+      <c r="G28" s="20" t="n">
         <f aca="false">1000/E28</f>
         <v>1351.35135135135</v>
       </c>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19" t="n">
+      <c r="H28" s="20"/>
+      <c r="I28" s="20" t="n">
         <f aca="false">0.68*1000</f>
         <v>680</v>
       </c>
-      <c r="J28" s="16"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="22"/>
-      <c r="X28" s="22"/>
-      <c r="Y28" s="22"/>
-      <c r="Z28" s="22"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="22"/>
-      <c r="AC28" s="22"/>
-      <c r="AD28" s="23"/>
+      <c r="J28" s="17"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="23"/>
+      <c r="X28" s="23"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="23"/>
+      <c r="AA28" s="23"/>
+      <c r="AB28" s="23"/>
+      <c r="AC28" s="23"/>
+      <c r="AD28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14"/>
-      <c r="C29" s="18" t="n">
+      <c r="B29" s="15"/>
+      <c r="C29" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18" t="n">
+      <c r="D29" s="19"/>
+      <c r="E29" s="19" t="n">
         <f aca="false">C29*$E$16</f>
         <v>0.925</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19" t="n">
+      <c r="F29" s="20"/>
+      <c r="G29" s="20" t="n">
         <f aca="false">1000/E29</f>
         <v>1081.08108108108</v>
       </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19" t="n">
+      <c r="H29" s="20"/>
+      <c r="I29" s="20" t="n">
         <f aca="false">0.52*1000</f>
         <v>520</v>
       </c>
-      <c r="J29" s="16"/>
-      <c r="V29" s="19"/>
-      <c r="W29" s="38"/>
-      <c r="X29" s="38"/>
-      <c r="Y29" s="38"/>
-      <c r="Z29" s="38"/>
-      <c r="AA29" s="38"/>
-      <c r="AB29" s="38"/>
-      <c r="AC29" s="19"/>
-      <c r="AD29" s="19"/>
+      <c r="J29" s="17"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="39"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="39"/>
+      <c r="AB29" s="39"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="14"/>
-      <c r="C30" s="18" t="n">
+      <c r="B30" s="15"/>
+      <c r="C30" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18" t="n">
+      <c r="D30" s="19"/>
+      <c r="E30" s="19" t="n">
         <f aca="false">C30*$E$16</f>
         <v>1.11</v>
       </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19" t="n">
+      <c r="F30" s="20"/>
+      <c r="G30" s="20" t="n">
         <f aca="false">1000/E30</f>
         <v>900.900900900901</v>
       </c>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19" t="n">
+      <c r="H30" s="20"/>
+      <c r="I30" s="20" t="n">
         <f aca="false">0.45*1000</f>
         <v>450</v>
       </c>
-      <c r="J30" s="16"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="39"/>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="39"/>
-      <c r="Z30" s="39"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="32"/>
-      <c r="AD30" s="19"/>
+      <c r="J30" s="17"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="40"/>
+      <c r="X30" s="40"/>
+      <c r="Y30" s="40"/>
+      <c r="Z30" s="40"/>
+      <c r="AA30" s="19"/>
+      <c r="AB30" s="19"/>
+      <c r="AC30" s="33"/>
+      <c r="AD30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14"/>
-      <c r="C31" s="18" t="n">
+      <c r="B31" s="15"/>
+      <c r="C31" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18" t="n">
+      <c r="D31" s="19"/>
+      <c r="E31" s="19" t="n">
         <f aca="false">C31*$E$16</f>
         <v>1.295</v>
       </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19" t="n">
+      <c r="F31" s="20"/>
+      <c r="G31" s="20" t="n">
         <f aca="false">1000/E31</f>
         <v>772.200772200772</v>
       </c>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19" t="n">
+      <c r="H31" s="20"/>
+      <c r="I31" s="20" t="n">
         <f aca="false">0.38*1000</f>
         <v>380</v>
       </c>
-      <c r="J31" s="16"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="19"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="19"/>
-      <c r="Z31" s="19"/>
-      <c r="AA31" s="19"/>
-      <c r="AB31" s="19"/>
-      <c r="AC31" s="19"/>
-      <c r="AD31" s="19"/>
+      <c r="J31" s="17"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="20"/>
+      <c r="AD31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14"/>
-      <c r="C32" s="18" t="n">
+      <c r="B32" s="15"/>
+      <c r="C32" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18" t="n">
+      <c r="D32" s="19"/>
+      <c r="E32" s="19" t="n">
         <f aca="false">C32*$E$16</f>
         <v>1.48</v>
       </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19" t="n">
+      <c r="F32" s="20"/>
+      <c r="G32" s="20" t="n">
         <f aca="false">1000/E32</f>
         <v>675.675675675676</v>
       </c>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19" t="n">
+      <c r="H32" s="20"/>
+      <c r="I32" s="20" t="n">
         <f aca="false">0.35*1000</f>
         <v>350</v>
       </c>
-      <c r="J32" s="16"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="38"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="19"/>
-      <c r="Z32" s="19"/>
-      <c r="AA32" s="19"/>
-      <c r="AB32" s="19"/>
-      <c r="AC32" s="19"/>
-      <c r="AD32" s="19"/>
+      <c r="J32" s="17"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="39"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
+      <c r="AC32" s="20"/>
+      <c r="AD32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="14"/>
-      <c r="C33" s="18" t="n">
+      <c r="B33" s="15"/>
+      <c r="C33" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18" t="n">
+      <c r="D33" s="19"/>
+      <c r="E33" s="19" t="n">
         <f aca="false">C33*$E$16</f>
         <v>1.665</v>
       </c>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19" t="n">
+      <c r="F33" s="20"/>
+      <c r="G33" s="20" t="n">
         <f aca="false">1000/E33</f>
         <v>600.600600600601</v>
       </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19" t="n">
+      <c r="H33" s="20"/>
+      <c r="I33" s="20" t="n">
         <f aca="false">0.31*1000</f>
         <v>310</v>
       </c>
-      <c r="J33" s="16"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="19"/>
-      <c r="X33" s="19"/>
-      <c r="Y33" s="19"/>
-      <c r="Z33" s="19"/>
-      <c r="AA33" s="19"/>
-      <c r="AB33" s="19"/>
-      <c r="AC33" s="19"/>
-      <c r="AD33" s="19"/>
+      <c r="J33" s="17"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="20"/>
+      <c r="AA33" s="20"/>
+      <c r="AB33" s="20"/>
+      <c r="AC33" s="20"/>
+      <c r="AD33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="14"/>
-      <c r="C34" s="18" t="n">
+      <c r="B34" s="15"/>
+      <c r="C34" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18" t="n">
+      <c r="D34" s="19"/>
+      <c r="E34" s="19" t="n">
         <f aca="false">C34*$E$16</f>
         <v>1.85</v>
       </c>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19" t="n">
+      <c r="F34" s="20"/>
+      <c r="G34" s="20" t="n">
         <f aca="false">1000/E34</f>
         <v>540.540540540541</v>
       </c>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19" t="n">
+      <c r="H34" s="20"/>
+      <c r="I34" s="20" t="n">
         <f aca="false">0.29*1000</f>
         <v>290</v>
       </c>
-      <c r="J34" s="16"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="40"/>
-      <c r="X34" s="41"/>
-      <c r="Y34" s="33"/>
-      <c r="Z34" s="18"/>
-      <c r="AA34" s="18"/>
-      <c r="AB34" s="19"/>
-      <c r="AC34" s="19"/>
-      <c r="AD34" s="19"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="20"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="23"/>
-      <c r="V35" s="19"/>
-      <c r="W35" s="19"/>
-      <c r="X35" s="19"/>
-      <c r="Y35" s="19"/>
-      <c r="Z35" s="19"/>
-      <c r="AA35" s="19"/>
-      <c r="AB35" s="19"/>
-      <c r="AC35" s="19"/>
-      <c r="AD35" s="19"/>
+      <c r="J34" s="17"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="41"/>
+      <c r="X34" s="42"/>
+      <c r="Y34" s="34"/>
+      <c r="Z34" s="19"/>
+      <c r="AA34" s="19"/>
+      <c r="AB34" s="20"/>
+      <c r="AC34" s="20"/>
+      <c r="AD34" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="21"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="24"/>
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+      <c r="Z35" s="20"/>
+      <c r="AA35" s="20"/>
+      <c r="AB35" s="20"/>
+      <c r="AC35" s="20"/>
+      <c r="AD35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="1"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
     </row>
     <row r="37" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D37" s="43"/>
-      <c r="E37" s="43" t="s">
+      <c r="D37" s="44"/>
+      <c r="E37" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
     </row>
     <row r="38" customFormat="false" ht="8.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D39" s="10"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="13"/>
-      <c r="V39" s="10"/>
-      <c r="W39" s="12"/>
-      <c r="X39" s="12"/>
-      <c r="Y39" s="12"/>
-      <c r="Z39" s="12"/>
-      <c r="AA39" s="12"/>
-      <c r="AB39" s="12"/>
-      <c r="AC39" s="12"/>
-      <c r="AD39" s="13"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="14"/>
+      <c r="V39" s="11"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="13"/>
+      <c r="AD39" s="14"/>
     </row>
     <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D40" s="14"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="45"/>
-      <c r="V40" s="14"/>
-      <c r="W40" s="30" t="s">
+      <c r="D40" s="15"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="46"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="19"/>
-      <c r="AB40" s="19"/>
-      <c r="AC40" s="19"/>
-      <c r="AD40" s="16"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="31"/>
+      <c r="AA40" s="20"/>
+      <c r="AB40" s="20"/>
+      <c r="AC40" s="20"/>
+      <c r="AD40" s="17"/>
     </row>
     <row r="41" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D41" s="14"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="16"/>
-      <c r="V41" s="14"/>
-      <c r="W41" s="31"/>
-      <c r="X41" s="31"/>
-      <c r="Y41" s="31"/>
-      <c r="Z41" s="31"/>
-      <c r="AA41" s="19"/>
-      <c r="AB41" s="19"/>
-      <c r="AC41" s="19"/>
-      <c r="AD41" s="16"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="17"/>
+      <c r="V41" s="15"/>
+      <c r="W41" s="32"/>
+      <c r="X41" s="32"/>
+      <c r="Y41" s="32"/>
+      <c r="Z41" s="32"/>
+      <c r="AA41" s="20"/>
+      <c r="AB41" s="20"/>
+      <c r="AC41" s="20"/>
+      <c r="AD41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D42" s="14"/>
-      <c r="E42" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F42" s="18"/>
-      <c r="G42" s="21" t="s">
+      <c r="C42" s="0"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="H42" s="19"/>
-      <c r="I42" s="22" t="s">
+      <c r="F42" s="19"/>
+      <c r="G42" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" s="20"/>
+      <c r="I42" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="J42" s="16"/>
-      <c r="V42" s="14"/>
-      <c r="W42" s="32" t="s">
+      <c r="J42" s="17"/>
+      <c r="V42" s="15"/>
+      <c r="W42" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="X42" s="33"/>
-      <c r="Y42" s="33"/>
-      <c r="Z42" s="18"/>
-      <c r="AA42" s="19"/>
-      <c r="AB42" s="19"/>
-      <c r="AC42" s="19"/>
-      <c r="AD42" s="16"/>
+      <c r="X42" s="34"/>
+      <c r="Y42" s="34"/>
+      <c r="Z42" s="19"/>
+      <c r="AA42" s="20"/>
+      <c r="AB42" s="20"/>
+      <c r="AC42" s="20"/>
+      <c r="AD42" s="17"/>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D43" s="14"/>
-      <c r="E43" s="18" t="n">
-        <f aca="false">$E$8+G43</f>
-        <v>0.275</v>
-      </c>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18" t="n">
-        <f aca="false">2/100</f>
-        <v>0.02</v>
-      </c>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19" t="n">
+      <c r="C43" s="0"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="19" t="n">
+        <f aca="false">$E$16*2</f>
+        <v>0.37</v>
+      </c>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G43) - 44) + 3)/100)</f>
+        <v>0.235</v>
+      </c>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20" t="n">
         <f aca="false">2.76*1000</f>
         <v>2760</v>
       </c>
-      <c r="J43" s="16"/>
-      <c r="V43" s="14"/>
-      <c r="W43" s="33"/>
-      <c r="X43" s="33"/>
-      <c r="Y43" s="33"/>
-      <c r="Z43" s="18"/>
-      <c r="AA43" s="19"/>
-      <c r="AB43" s="19"/>
-      <c r="AC43" s="19"/>
-      <c r="AD43" s="16"/>
+      <c r="J43" s="17"/>
+      <c r="V43" s="15"/>
+      <c r="W43" s="34"/>
+      <c r="X43" s="34"/>
+      <c r="Y43" s="34"/>
+      <c r="Z43" s="19"/>
+      <c r="AA43" s="20"/>
+      <c r="AB43" s="20"/>
+      <c r="AC43" s="20"/>
+      <c r="AD43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D44" s="14"/>
-      <c r="E44" s="18" t="n">
-        <f aca="false">$E$8+G44</f>
-        <v>0.285</v>
-      </c>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18" t="n">
-        <f aca="false">G43+0.01</f>
-        <v>0.03</v>
-      </c>
-      <c r="H44" s="19"/>
-      <c r="I44" s="0" t="n">
+      <c r="C44" s="0"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="19" t="n">
+        <f aca="false">$E$16*2</f>
+        <v>0.37</v>
+      </c>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G44) - 44) + 3)/100)</f>
+        <v>0.225</v>
+      </c>
+      <c r="H44" s="20"/>
+      <c r="I44" s="1" t="n">
         <f aca="false">2.68*1000</f>
         <v>2680</v>
       </c>
-      <c r="J44" s="16"/>
-      <c r="V44" s="14"/>
-      <c r="W44" s="34" t="s">
+      <c r="J44" s="17"/>
+      <c r="V44" s="15"/>
+      <c r="W44" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="X44" s="33" t="s">
+      <c r="X44" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="Y44" s="35" t="s">
+      <c r="Y44" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="Z44" s="33" t="s">
+      <c r="Z44" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AA44" s="22"/>
-      <c r="AB44" s="33" t="s">
+      <c r="AA44" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB44" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AC44" s="36"/>
-      <c r="AD44" s="16"/>
+      <c r="AC44" s="37" t="n">
+        <f aca="false">(E43/1000)*SLOPE(I43:I52,G43:G52)/(8.854 * 0.255)</f>
+        <v>2.1343935374151</v>
+      </c>
+      <c r="AD44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D45" s="14"/>
-      <c r="E45" s="18" t="n">
-        <f aca="false">$E$8+G45</f>
-        <v>0.295</v>
-      </c>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18" t="n">
-        <f aca="false">G44+0.01</f>
-        <v>0.04</v>
-      </c>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19" t="n">
+      <c r="C45" s="0"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="19" t="n">
+        <f aca="false">$E$16*2</f>
+        <v>0.37</v>
+      </c>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G45) - 44) + 3)/100)</f>
+        <v>0.215</v>
+      </c>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20" t="n">
         <f aca="false">2.41*1000</f>
         <v>2410</v>
       </c>
-      <c r="J45" s="16"/>
-      <c r="V45" s="14"/>
-      <c r="W45" s="34"/>
-      <c r="X45" s="33"/>
-      <c r="Y45" s="37" t="s">
+      <c r="J45" s="17"/>
+      <c r="V45" s="15"/>
+      <c r="W45" s="35"/>
+      <c r="X45" s="34"/>
+      <c r="Y45" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="Z45" s="33"/>
-      <c r="AA45" s="19"/>
-      <c r="AB45" s="33"/>
-      <c r="AC45" s="36"/>
-      <c r="AD45" s="16"/>
+      <c r="Z45" s="34"/>
+      <c r="AA45" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB45" s="34"/>
+      <c r="AC45" s="37"/>
+      <c r="AD45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D46" s="14"/>
-      <c r="E46" s="18" t="n">
-        <f aca="false">$E$8+G46</f>
-        <v>0.305</v>
-      </c>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18" t="n">
-        <f aca="false">G45+0.01</f>
-        <v>0.05</v>
-      </c>
-      <c r="H46" s="19"/>
-      <c r="I46" s="0" t="n">
+      <c r="C46" s="0"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="19" t="n">
+        <f aca="false">$E$16*2</f>
+        <v>0.37</v>
+      </c>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G46) - 44) + 3)/100)</f>
+        <v>0.205</v>
+      </c>
+      <c r="H46" s="20"/>
+      <c r="I46" s="1" t="n">
         <f aca="false">2.45*1000</f>
         <v>2450</v>
       </c>
-      <c r="J46" s="16"/>
-      <c r="V46" s="20"/>
-      <c r="W46" s="22"/>
-      <c r="X46" s="22"/>
-      <c r="Y46" s="22"/>
-      <c r="Z46" s="22"/>
-      <c r="AA46" s="22"/>
-      <c r="AB46" s="22"/>
-      <c r="AC46" s="22"/>
-      <c r="AD46" s="23"/>
+      <c r="J46" s="17"/>
+      <c r="V46" s="21"/>
+      <c r="W46" s="23"/>
+      <c r="X46" s="23"/>
+      <c r="Y46" s="23"/>
+      <c r="Z46" s="23"/>
+      <c r="AA46" s="23"/>
+      <c r="AB46" s="23"/>
+      <c r="AC46" s="23"/>
+      <c r="AD46" s="24"/>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D47" s="14"/>
-      <c r="E47" s="18" t="n">
-        <f aca="false">$E$8+G47</f>
-        <v>0.315</v>
-      </c>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18" t="n">
-        <f aca="false">G46+0.01</f>
-        <v>0.06</v>
-      </c>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19" t="n">
+      <c r="C47" s="0"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="19" t="n">
+        <f aca="false">$E$16*2</f>
+        <v>0.37</v>
+      </c>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G47) - 44) + 3)/100)</f>
+        <v>0.195</v>
+      </c>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20" t="n">
         <f aca="false">2.27*1000</f>
         <v>2270</v>
       </c>
-      <c r="J47" s="16"/>
-      <c r="V47" s="19"/>
-      <c r="W47" s="38"/>
-      <c r="X47" s="38"/>
-      <c r="Y47" s="38"/>
-      <c r="Z47" s="38"/>
-      <c r="AA47" s="38"/>
-      <c r="AB47" s="38"/>
-      <c r="AC47" s="19"/>
-      <c r="AD47" s="19"/>
+      <c r="J47" s="17"/>
+      <c r="V47" s="20"/>
+      <c r="W47" s="39"/>
+      <c r="X47" s="39"/>
+      <c r="Y47" s="39"/>
+      <c r="Z47" s="39"/>
+      <c r="AA47" s="39"/>
+      <c r="AB47" s="39"/>
+      <c r="AC47" s="20"/>
+      <c r="AD47" s="20"/>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D48" s="14"/>
-      <c r="E48" s="18" t="n">
-        <f aca="false">$E$8+G48</f>
-        <v>0.325</v>
-      </c>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18" t="n">
-        <f aca="false">G47+0.01</f>
-        <v>0.07</v>
-      </c>
-      <c r="H48" s="19"/>
-      <c r="I48" s="0" t="n">
+      <c r="C48" s="0"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="19" t="n">
+        <f aca="false">$E$16*2</f>
+        <v>0.37</v>
+      </c>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G48) - 44) + 3)/100)</f>
+        <v>0.185</v>
+      </c>
+      <c r="H48" s="20"/>
+      <c r="I48" s="1" t="n">
         <f aca="false">2.2*1000</f>
         <v>2200</v>
       </c>
-      <c r="J48" s="16"/>
-      <c r="V48" s="19"/>
-      <c r="W48" s="39"/>
-      <c r="X48" s="39"/>
-      <c r="Y48" s="39"/>
-      <c r="Z48" s="39"/>
-      <c r="AA48" s="18"/>
-      <c r="AB48" s="18"/>
-      <c r="AC48" s="32"/>
-      <c r="AD48" s="19"/>
+      <c r="J48" s="17"/>
+      <c r="V48" s="20"/>
+      <c r="W48" s="40"/>
+      <c r="X48" s="40"/>
+      <c r="Y48" s="40"/>
+      <c r="Z48" s="40"/>
+      <c r="AA48" s="19"/>
+      <c r="AB48" s="19"/>
+      <c r="AC48" s="33"/>
+      <c r="AD48" s="20"/>
     </row>
     <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D49" s="14"/>
-      <c r="E49" s="18" t="n">
-        <f aca="false">$E$8+G49</f>
-        <v>0.335</v>
-      </c>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18" t="n">
-        <f aca="false">G48+0.01</f>
-        <v>0.08</v>
-      </c>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19" t="n">
+      <c r="C49" s="0"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="19" t="n">
+        <f aca="false">$E$16*2</f>
+        <v>0.37</v>
+      </c>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G49) - 44) + 3)/100)</f>
+        <v>0.175</v>
+      </c>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20" t="n">
         <f aca="false">2.1*1000</f>
         <v>2100</v>
       </c>
-      <c r="J49" s="16"/>
-      <c r="V49" s="19"/>
-      <c r="W49" s="19"/>
-      <c r="X49" s="19"/>
-      <c r="Y49" s="19"/>
-      <c r="Z49" s="19"/>
-      <c r="AA49" s="19"/>
-      <c r="AB49" s="19"/>
-      <c r="AC49" s="19"/>
-      <c r="AD49" s="19"/>
+      <c r="J49" s="17"/>
+      <c r="V49" s="20"/>
+      <c r="W49" s="20"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
+      <c r="Z49" s="20"/>
+      <c r="AA49" s="20"/>
+      <c r="AB49" s="20"/>
+      <c r="AC49" s="20"/>
+      <c r="AD49" s="20"/>
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D50" s="14"/>
-      <c r="E50" s="18" t="n">
-        <f aca="false">$E$8+G50</f>
-        <v>0.345</v>
-      </c>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18" t="n">
-        <f aca="false">G49+0.01</f>
-        <v>0.09</v>
-      </c>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19" t="n">
+      <c r="C50" s="0"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="19" t="n">
+        <f aca="false">$E$16*2</f>
+        <v>0.37</v>
+      </c>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G50) - 44) + 3)/100)</f>
+        <v>0.165</v>
+      </c>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20" t="n">
         <f aca="false">1.72*1000</f>
         <v>1720</v>
       </c>
-      <c r="J50" s="16"/>
-      <c r="V50" s="19"/>
-      <c r="W50" s="38"/>
-      <c r="X50" s="19"/>
-      <c r="Y50" s="19"/>
-      <c r="Z50" s="19"/>
-      <c r="AA50" s="19"/>
-      <c r="AB50" s="19"/>
-      <c r="AC50" s="19"/>
-      <c r="AD50" s="19"/>
+      <c r="J50" s="17"/>
+      <c r="V50" s="20"/>
+      <c r="W50" s="39"/>
+      <c r="X50" s="20"/>
+      <c r="Y50" s="20"/>
+      <c r="Z50" s="20"/>
+      <c r="AA50" s="20"/>
+      <c r="AB50" s="20"/>
+      <c r="AC50" s="20"/>
+      <c r="AD50" s="20"/>
     </row>
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D51" s="14"/>
-      <c r="E51" s="18" t="n">
-        <f aca="false">$E$8+G51</f>
-        <v>0.355</v>
-      </c>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18" t="n">
-        <f aca="false">G50+0.01</f>
-        <v>0.1</v>
-      </c>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19" t="n">
+      <c r="C51" s="0"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="19" t="n">
+        <f aca="false">$E$16*2</f>
+        <v>0.37</v>
+      </c>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G51) - 44) + 3)/100)</f>
+        <v>0.155</v>
+      </c>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20" t="n">
         <f aca="false">1.6*1000</f>
         <v>1600</v>
       </c>
-      <c r="J51" s="16"/>
-      <c r="V51" s="19"/>
-      <c r="W51" s="19"/>
-      <c r="X51" s="19"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="19"/>
-      <c r="AA51" s="19"/>
-      <c r="AB51" s="19"/>
-      <c r="AC51" s="19"/>
-      <c r="AD51" s="19"/>
+      <c r="J51" s="17"/>
+      <c r="V51" s="20"/>
+      <c r="W51" s="20"/>
+      <c r="X51" s="20"/>
+      <c r="Y51" s="20"/>
+      <c r="Z51" s="20"/>
+      <c r="AA51" s="20"/>
+      <c r="AB51" s="20"/>
+      <c r="AC51" s="20"/>
+      <c r="AD51" s="20"/>
     </row>
     <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D52" s="14"/>
-      <c r="E52" s="18" t="n">
-        <f aca="false">$E$8+G52</f>
-        <v>0.365</v>
-      </c>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18" t="n">
-        <f aca="false">G51+0.01</f>
-        <v>0.11</v>
-      </c>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19" t="n">
+      <c r="C52" s="0"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="19" t="n">
+        <f aca="false">$E$16*2</f>
+        <v>0.37</v>
+      </c>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G52) - 44) + 3)/100)</f>
+        <v>0.145</v>
+      </c>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20" t="n">
         <f aca="false">1.72*1000</f>
         <v>1720</v>
       </c>
-      <c r="J52" s="16"/>
-      <c r="V52" s="19"/>
-      <c r="W52" s="40"/>
-      <c r="X52" s="41"/>
-      <c r="Y52" s="33"/>
-      <c r="Z52" s="18"/>
-      <c r="AA52" s="18"/>
-      <c r="AB52" s="19"/>
-      <c r="AC52" s="19"/>
-      <c r="AD52" s="19"/>
-    </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D53" s="20"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="23"/>
-      <c r="V53" s="19"/>
-      <c r="W53" s="19"/>
-      <c r="X53" s="19"/>
-      <c r="Y53" s="19"/>
-      <c r="Z53" s="19"/>
-      <c r="AA53" s="19"/>
-      <c r="AB53" s="19"/>
-      <c r="AC53" s="19"/>
-      <c r="AD53" s="19"/>
+      <c r="J52" s="17"/>
+      <c r="V52" s="20"/>
+      <c r="W52" s="41"/>
+      <c r="X52" s="42"/>
+      <c r="Y52" s="34"/>
+      <c r="Z52" s="19"/>
+      <c r="AA52" s="19"/>
+      <c r="AB52" s="20"/>
+      <c r="AC52" s="20"/>
+      <c r="AD52" s="20"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D53" s="21"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="23"/>
+      <c r="I53" s="23"/>
+      <c r="J53" s="24"/>
+      <c r="V53" s="20"/>
+      <c r="W53" s="20"/>
+      <c r="X53" s="20"/>
+      <c r="Y53" s="20"/>
+      <c r="Z53" s="20"/>
+      <c r="AA53" s="20"/>
+      <c r="AB53" s="20"/>
+      <c r="AC53" s="20"/>
+      <c r="AD53" s="20"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="1"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -4263,1038 +5044,1054 @@
   <dimension ref="B1:AD1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="13" style="0" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="2.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="7.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="2.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="13" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="2.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="7.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="3.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="2.29"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14"/>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="14"/>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <f aca="false">25.5/100</f>
         <v>0.255</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19" t="n">
+      <c r="F8" s="20"/>
+      <c r="G8" s="20" t="n">
         <v>0.255</v>
       </c>
-      <c r="H8" s="16"/>
+      <c r="H8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="14"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">10.2/100</f>
         <v>0.102</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19" t="n">
+      <c r="F9" s="20"/>
+      <c r="G9" s="20" t="n">
         <v>0.102</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="23"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="19"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="14"/>
-      <c r="C13" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="19"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="14"/>
-      <c r="C14" s="25" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18" t="n">
+      <c r="D14" s="26"/>
+      <c r="E14" s="19" t="n">
         <v>112</v>
       </c>
-      <c r="F14" s="26"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="19"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="14"/>
-      <c r="C15" s="25" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="46" t="n">
+      <c r="D15" s="26"/>
+      <c r="E15" s="47" t="n">
         <v>2.64</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="19"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="14"/>
-      <c r="C16" s="25" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="47" t="n">
+      <c r="D16" s="26"/>
+      <c r="E16" s="48" t="n">
         <f aca="false">E15/E14</f>
         <v>0.0235714285714286</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="19"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" customFormat="false" ht="8.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="13"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
-      <c r="AA21" s="12"/>
-      <c r="AB21" s="12"/>
-      <c r="AC21" s="12"/>
-      <c r="AD21" s="13"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="14"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14"/>
-      <c r="C22" s="29" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="16"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="30" t="s">
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="17"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="19"/>
-      <c r="AB22" s="19"/>
-      <c r="AC22" s="19"/>
-      <c r="AD22" s="16"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="16"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="19"/>
-      <c r="AB23" s="19"/>
-      <c r="AC23" s="19"/>
-      <c r="AD23" s="16"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="17"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14"/>
-      <c r="C24" s="21" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="21" t="s">
+      <c r="D24" s="19"/>
+      <c r="E24" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="22" t="s">
+      <c r="F24" s="20"/>
+      <c r="G24" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="H24" s="19"/>
-      <c r="I24" s="22" t="s">
+      <c r="H24" s="20"/>
+      <c r="I24" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="16"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="32" t="s">
+      <c r="J24" s="17"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="X24" s="33"/>
-      <c r="Y24" s="33"/>
-      <c r="Z24" s="18"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="19"/>
-      <c r="AC24" s="19"/>
-      <c r="AD24" s="16"/>
+      <c r="X24" s="34"/>
+      <c r="Y24" s="34"/>
+      <c r="Z24" s="19"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AD24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="14"/>
-      <c r="C25" s="18" t="n">
+      <c r="B25" s="15"/>
+      <c r="C25" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18" t="n">
+      <c r="D25" s="19"/>
+      <c r="E25" s="49" t="n">
         <f aca="false">C25*$E$16</f>
         <v>0.0235714285714286</v>
       </c>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19" t="n">
+      <c r="F25" s="20"/>
+      <c r="G25" s="50" t="n">
         <f aca="false">1000/E25</f>
         <v>42424.2424242424</v>
       </c>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19" t="n">
+      <c r="H25" s="20"/>
+      <c r="I25" s="20" t="n">
         <f aca="false">15*1000</f>
         <v>15000</v>
       </c>
-      <c r="J25" s="16"/>
-      <c r="K25" s="0" t="n">
+      <c r="J25" s="17"/>
+      <c r="K25" s="1" t="n">
         <f aca="false">SLOPE(I25:I32,G25:G32)</f>
         <v>0.359279303839435</v>
       </c>
-      <c r="L25" s="0" t="n">
+      <c r="L25" s="1" t="n">
         <f aca="false">G25*$K$25+$K$26</f>
         <v>14908.903226866</v>
       </c>
-      <c r="M25" s="48" t="n">
+      <c r="M25" s="51" t="n">
         <f aca="false">(L25-I25)/L25</f>
         <v>-0.0061102263357546</v>
       </c>
-      <c r="V25" s="14"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="33"/>
-      <c r="Y25" s="33"/>
-      <c r="Z25" s="18"/>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="16"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="34"/>
+      <c r="X25" s="34"/>
+      <c r="Y25" s="34"/>
+      <c r="Z25" s="19"/>
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="20"/>
+      <c r="AD25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="14"/>
-      <c r="C26" s="18" t="n">
+      <c r="B26" s="15"/>
+      <c r="C26" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18" t="n">
+      <c r="D26" s="19"/>
+      <c r="E26" s="49" t="n">
         <f aca="false">C26*$E$16</f>
         <v>0.0471428571428571</v>
       </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19" t="n">
+      <c r="F26" s="20"/>
+      <c r="G26" s="50" t="n">
         <f aca="false">1000/E26</f>
         <v>21212.1212121212</v>
       </c>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19" t="n">
+      <c r="H26" s="20"/>
+      <c r="I26" s="20" t="n">
         <f aca="false">7.01*1000</f>
         <v>7010</v>
       </c>
-      <c r="J26" s="16"/>
-      <c r="K26" s="0" t="n">
+      <c r="J26" s="17"/>
+      <c r="K26" s="1" t="n">
         <f aca="false">INTERCEPT(I25:I32,G25:G32)</f>
         <v>-333.249057231246</v>
       </c>
-      <c r="L26" s="0" t="n">
+      <c r="L26" s="1" t="n">
         <f aca="false">G26*$K$25+$K$26</f>
         <v>7287.82708481737</v>
       </c>
-      <c r="M26" s="48" t="n">
+      <c r="M26" s="51" t="n">
         <f aca="false">(L26-I26)/L26</f>
         <v>0.0381220741908329</v>
       </c>
-      <c r="V26" s="14"/>
-      <c r="W26" s="34" t="s">
+      <c r="V26" s="15"/>
+      <c r="W26" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="X26" s="33" t="s">
+      <c r="X26" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="Y26" s="35" t="s">
+      <c r="Y26" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="Z26" s="33" t="s">
+      <c r="Z26" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AA26" s="22"/>
-      <c r="AB26" s="33" t="s">
+      <c r="AA26" s="52" t="str">
+        <f aca="false">TEXT(SLOPE(I25:I32,G25:G32), "0.000")</f>
+        <v>0.359</v>
+      </c>
+      <c r="AB26" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AC26" s="36"/>
-      <c r="AD26" s="16"/>
+      <c r="AC26" s="37" t="n">
+        <f aca="false">SLOPE(I25:I32,G25:G32)/(8.8541*E9*E8)</f>
+        <v>1.56008199860124</v>
+      </c>
+      <c r="AD26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14"/>
-      <c r="C27" s="18" t="n">
+      <c r="B27" s="15"/>
+      <c r="C27" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18" t="n">
+      <c r="D27" s="19"/>
+      <c r="E27" s="49" t="n">
         <f aca="false">C27*$E$16</f>
         <v>0.0707142857142857</v>
       </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19" t="n">
+      <c r="F27" s="20"/>
+      <c r="G27" s="50" t="n">
         <f aca="false">1000/E27</f>
         <v>14141.4141414141</v>
       </c>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19" t="n">
+      <c r="H27" s="20"/>
+      <c r="I27" s="20" t="n">
         <f aca="false">4.94*1000</f>
         <v>4940</v>
       </c>
-      <c r="J27" s="16"/>
-      <c r="L27" s="0" t="n">
+      <c r="J27" s="17"/>
+      <c r="L27" s="1" t="n">
         <f aca="false">G27*$K$25+$K$26</f>
         <v>4747.46837080115</v>
       </c>
-      <c r="M27" s="48" t="n">
+      <c r="M27" s="51" t="n">
         <f aca="false">(L27-I27)/L27</f>
         <v>-0.0405545891328067</v>
       </c>
-      <c r="V27" s="14"/>
-      <c r="W27" s="34"/>
-      <c r="X27" s="33"/>
-      <c r="Y27" s="37" t="s">
+      <c r="V27" s="15"/>
+      <c r="W27" s="35"/>
+      <c r="X27" s="34"/>
+      <c r="Y27" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="Z27" s="33"/>
-      <c r="AA27" s="19"/>
-      <c r="AB27" s="33"/>
-      <c r="AC27" s="36"/>
-      <c r="AD27" s="16"/>
+      <c r="Z27" s="34"/>
+      <c r="AA27" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB27" s="34"/>
+      <c r="AC27" s="37"/>
+      <c r="AD27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="14"/>
-      <c r="C28" s="18" t="n">
+      <c r="B28" s="15"/>
+      <c r="C28" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18" t="n">
+      <c r="D28" s="19"/>
+      <c r="E28" s="49" t="n">
         <f aca="false">C28*$E$16</f>
         <v>0.0942857142857143</v>
       </c>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19" t="n">
+      <c r="F28" s="20"/>
+      <c r="G28" s="50" t="n">
         <f aca="false">1000/E28</f>
         <v>10606.0606060606</v>
       </c>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19" t="n">
+      <c r="H28" s="20"/>
+      <c r="I28" s="20" t="n">
         <f aca="false">3.4*1000</f>
         <v>3400</v>
       </c>
-      <c r="J28" s="16"/>
-      <c r="L28" s="0" t="n">
+      <c r="J28" s="17"/>
+      <c r="L28" s="1" t="n">
         <f aca="false">G28*$K$25+$K$26</f>
         <v>3477.28901379306</v>
       </c>
-      <c r="M28" s="48" t="n">
+      <c r="M28" s="51" t="n">
         <f aca="false">(L28-I28)/L28</f>
         <v>0.022226801823629</v>
       </c>
-      <c r="V28" s="20"/>
-      <c r="W28" s="22"/>
-      <c r="X28" s="22"/>
-      <c r="Y28" s="22"/>
-      <c r="Z28" s="22"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="22"/>
-      <c r="AC28" s="22"/>
-      <c r="AD28" s="23"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="23"/>
+      <c r="X28" s="23"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="23"/>
+      <c r="AA28" s="23"/>
+      <c r="AB28" s="23"/>
+      <c r="AC28" s="23"/>
+      <c r="AD28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14"/>
-      <c r="C29" s="18" t="n">
+      <c r="B29" s="15"/>
+      <c r="C29" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18" t="n">
+      <c r="D29" s="19"/>
+      <c r="E29" s="49" t="n">
         <f aca="false">C29*$E$16</f>
         <v>0.117857142857143</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19" t="n">
+      <c r="F29" s="20"/>
+      <c r="G29" s="50" t="n">
         <f aca="false">1000/E29</f>
         <v>8484.84848484848</v>
       </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19" t="n">
+      <c r="H29" s="20"/>
+      <c r="I29" s="20" t="n">
         <f aca="false">2.55*1000</f>
         <v>2550</v>
       </c>
-      <c r="J29" s="16"/>
-      <c r="L29" s="0" t="n">
+      <c r="J29" s="17"/>
+      <c r="L29" s="1" t="n">
         <f aca="false">G29*$K$25+$K$26</f>
         <v>2715.1813995882</v>
       </c>
-      <c r="M29" s="48" t="n">
+      <c r="M29" s="51" t="n">
         <f aca="false">(L29-I29)/L29</f>
         <v>0.0608362298052172</v>
       </c>
-      <c r="V29" s="19"/>
-      <c r="W29" s="38"/>
-      <c r="X29" s="38"/>
-      <c r="Y29" s="38"/>
-      <c r="Z29" s="38"/>
-      <c r="AA29" s="38"/>
-      <c r="AB29" s="38"/>
-      <c r="AC29" s="19"/>
-      <c r="AD29" s="19"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="39"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="39"/>
+      <c r="AB29" s="39"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="14"/>
-      <c r="C30" s="18" t="n">
+      <c r="B30" s="15"/>
+      <c r="C30" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18" t="n">
+      <c r="D30" s="19"/>
+      <c r="E30" s="49" t="n">
         <f aca="false">C30*$E$16</f>
         <v>0.141428571428571</v>
       </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19" t="n">
+      <c r="F30" s="20"/>
+      <c r="G30" s="50" t="n">
         <f aca="false">1000/E30</f>
         <v>7070.70707070707</v>
       </c>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19" t="n">
+      <c r="H30" s="20"/>
+      <c r="I30" s="20" t="n">
         <f aca="false">2.38*1000</f>
         <v>2380</v>
       </c>
-      <c r="J30" s="16"/>
-      <c r="L30" s="0" t="n">
+      <c r="J30" s="17"/>
+      <c r="L30" s="1" t="n">
         <f aca="false">G30*$K$25+$K$26</f>
         <v>2207.10965678496</v>
       </c>
-      <c r="M30" s="48" t="n">
+      <c r="M30" s="51" t="n">
         <f aca="false">(L30-I30)/L30</f>
         <v>-0.0783333726457828</v>
       </c>
-      <c r="V30" s="19"/>
-      <c r="W30" s="39"/>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="39"/>
-      <c r="Z30" s="39"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="32"/>
-      <c r="AD30" s="19"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="40"/>
+      <c r="X30" s="40"/>
+      <c r="Y30" s="40"/>
+      <c r="Z30" s="40"/>
+      <c r="AA30" s="19"/>
+      <c r="AB30" s="19"/>
+      <c r="AC30" s="33"/>
+      <c r="AD30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14"/>
-      <c r="C31" s="18" t="n">
+      <c r="B31" s="15"/>
+      <c r="C31" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18" t="n">
+      <c r="D31" s="19"/>
+      <c r="E31" s="49" t="n">
         <f aca="false">C31*$E$16</f>
         <v>0.165</v>
       </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19" t="n">
+      <c r="F31" s="20"/>
+      <c r="G31" s="50" t="n">
         <f aca="false">1000/E31</f>
         <v>6060.60606060606</v>
       </c>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19" t="n">
+      <c r="H31" s="20"/>
+      <c r="I31" s="20" t="n">
         <f aca="false">1.8*1000</f>
         <v>1800</v>
       </c>
-      <c r="J31" s="16"/>
-      <c r="L31" s="0" t="n">
+      <c r="J31" s="17"/>
+      <c r="L31" s="1" t="n">
         <f aca="false">G31*$K$25+$K$26</f>
         <v>1844.20126906836</v>
       </c>
-      <c r="M31" s="48" t="n">
+      <c r="M31" s="51" t="n">
         <f aca="false">(L31-I31)/L31</f>
         <v>0.0239677034224612</v>
       </c>
-      <c r="V31" s="19"/>
-      <c r="W31" s="19"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="19"/>
-      <c r="Z31" s="19"/>
-      <c r="AA31" s="19"/>
-      <c r="AB31" s="19"/>
-      <c r="AC31" s="19"/>
-      <c r="AD31" s="19"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="20"/>
+      <c r="AD31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14"/>
-      <c r="C32" s="18" t="n">
+      <c r="B32" s="15"/>
+      <c r="C32" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18" t="n">
+      <c r="D32" s="19"/>
+      <c r="E32" s="49" t="n">
         <f aca="false">C32*$E$16</f>
         <v>0.188571428571429</v>
       </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19" t="n">
+      <c r="F32" s="20"/>
+      <c r="G32" s="50" t="n">
         <f aca="false">1000/E32</f>
         <v>5303.0303030303</v>
       </c>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19" t="n">
+      <c r="H32" s="20"/>
+      <c r="I32" s="20" t="n">
         <f aca="false">1.68*1000</f>
         <v>1680</v>
       </c>
-      <c r="J32" s="16"/>
-      <c r="L32" s="0" t="n">
+      <c r="J32" s="17"/>
+      <c r="L32" s="1" t="n">
         <f aca="false">G32*$K$25+$K$26</f>
         <v>1572.01997828091</v>
       </c>
-      <c r="M32" s="48" t="n">
+      <c r="M32" s="51" t="n">
         <f aca="false">(L32-I32)/L32</f>
         <v>-0.0686887082931196</v>
       </c>
-      <c r="V32" s="19"/>
-      <c r="W32" s="38"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="19"/>
-      <c r="Z32" s="19"/>
-      <c r="AA32" s="19"/>
-      <c r="AB32" s="19"/>
-      <c r="AC32" s="19"/>
-      <c r="AD32" s="19"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="20"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="23"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="19"/>
-      <c r="X33" s="19"/>
-      <c r="Y33" s="19"/>
-      <c r="Z33" s="19"/>
-      <c r="AA33" s="19"/>
-      <c r="AB33" s="19"/>
-      <c r="AC33" s="19"/>
-      <c r="AD33" s="19"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="39"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
+      <c r="AC32" s="20"/>
+      <c r="AD32" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="21"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="24"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="20"/>
+      <c r="AA33" s="20"/>
+      <c r="AB33" s="20"/>
+      <c r="AC33" s="20"/>
+      <c r="AD33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="1"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
     </row>
     <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D35" s="43"/>
-      <c r="E35" s="43" t="s">
+      <c r="D35" s="44"/>
+      <c r="E35" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
     </row>
     <row r="36" customFormat="false" ht="8.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D37" s="10"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="13"/>
-      <c r="V37" s="10"/>
-      <c r="W37" s="12"/>
-      <c r="X37" s="12"/>
-      <c r="Y37" s="12"/>
-      <c r="Z37" s="12"/>
-      <c r="AA37" s="12"/>
-      <c r="AB37" s="12"/>
-      <c r="AC37" s="12"/>
-      <c r="AD37" s="13"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="14"/>
+      <c r="V37" s="11"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="13"/>
+      <c r="Z37" s="13"/>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="13"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="14"/>
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D38" s="14"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="45"/>
-      <c r="V38" s="14"/>
-      <c r="W38" s="30" t="s">
+      <c r="D38" s="15"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="46"/>
+      <c r="V38" s="15"/>
+      <c r="W38" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="X38" s="30"/>
-      <c r="Y38" s="30"/>
-      <c r="Z38" s="30"/>
-      <c r="AA38" s="19"/>
-      <c r="AB38" s="19"/>
-      <c r="AC38" s="19"/>
-      <c r="AD38" s="16"/>
+      <c r="X38" s="31"/>
+      <c r="Y38" s="31"/>
+      <c r="Z38" s="31"/>
+      <c r="AA38" s="20"/>
+      <c r="AB38" s="20"/>
+      <c r="AC38" s="20"/>
+      <c r="AD38" s="17"/>
     </row>
     <row r="39" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D39" s="14"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="16"/>
-      <c r="V39" s="14"/>
-      <c r="W39" s="31"/>
-      <c r="X39" s="31"/>
-      <c r="Y39" s="31"/>
-      <c r="Z39" s="31"/>
-      <c r="AA39" s="19"/>
-      <c r="AB39" s="19"/>
-      <c r="AC39" s="19"/>
-      <c r="AD39" s="16"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="17"/>
+      <c r="V39" s="15"/>
+      <c r="W39" s="32"/>
+      <c r="X39" s="32"/>
+      <c r="Y39" s="32"/>
+      <c r="Z39" s="32"/>
+      <c r="AA39" s="20"/>
+      <c r="AB39" s="20"/>
+      <c r="AC39" s="20"/>
+      <c r="AD39" s="17"/>
     </row>
     <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D40" s="14"/>
-      <c r="E40" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" s="18"/>
-      <c r="G40" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="H40" s="19"/>
-      <c r="I40" s="22" t="s">
+      <c r="D40" s="15"/>
+      <c r="E40" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" s="20"/>
+      <c r="I40" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="J40" s="16"/>
-      <c r="V40" s="14"/>
-      <c r="W40" s="32" t="s">
+      <c r="J40" s="17"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="X40" s="33"/>
-      <c r="Y40" s="33"/>
-      <c r="Z40" s="18"/>
-      <c r="AA40" s="19"/>
-      <c r="AB40" s="19"/>
-      <c r="AC40" s="19"/>
-      <c r="AD40" s="16"/>
+      <c r="X40" s="34"/>
+      <c r="Y40" s="34"/>
+      <c r="Z40" s="19"/>
+      <c r="AA40" s="20"/>
+      <c r="AB40" s="20"/>
+      <c r="AC40" s="20"/>
+      <c r="AD40" s="17"/>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D41" s="14"/>
-      <c r="E41" s="18" t="n">
-        <f aca="false">$E$8+G41</f>
+      <c r="D41" s="15"/>
+      <c r="E41" s="19" t="n">
+        <f aca="false">2*$E$8-G41</f>
         <v>0.275</v>
       </c>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18" t="n">
-        <f aca="false">2/100</f>
-        <v>0.02</v>
-      </c>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19" t="n">
+      <c r="F41" s="19"/>
+      <c r="G41" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G41) - 41) + 2)/100)</f>
+        <v>0.235</v>
+      </c>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20" t="n">
         <f aca="false">6.31*1000</f>
         <v>6310</v>
       </c>
-      <c r="J41" s="16"/>
-      <c r="V41" s="14"/>
-      <c r="W41" s="33"/>
-      <c r="X41" s="33"/>
-      <c r="Y41" s="33"/>
-      <c r="Z41" s="18"/>
-      <c r="AA41" s="19"/>
-      <c r="AB41" s="19"/>
-      <c r="AC41" s="19"/>
-      <c r="AD41" s="16"/>
+      <c r="J41" s="17"/>
+      <c r="V41" s="15"/>
+      <c r="W41" s="34"/>
+      <c r="X41" s="34"/>
+      <c r="Y41" s="34"/>
+      <c r="Z41" s="19"/>
+      <c r="AA41" s="20"/>
+      <c r="AB41" s="20"/>
+      <c r="AC41" s="20"/>
+      <c r="AD41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D42" s="14"/>
-      <c r="E42" s="18" t="n">
-        <f aca="false">$E$8+G42</f>
+      <c r="D42" s="15"/>
+      <c r="E42" s="19" t="n">
+        <f aca="false">2*$E$8-G42</f>
         <v>0.285</v>
       </c>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18" t="n">
-        <f aca="false">G41+0.01</f>
-        <v>0.03</v>
-      </c>
-      <c r="H42" s="19"/>
-      <c r="I42" s="0" t="n">
+      <c r="F42" s="19"/>
+      <c r="G42" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G42) - 41) + 2)/100)</f>
+        <v>0.225</v>
+      </c>
+      <c r="H42" s="20"/>
+      <c r="I42" s="1" t="n">
         <f aca="false">5.75*1000</f>
         <v>5750</v>
       </c>
-      <c r="J42" s="16"/>
-      <c r="V42" s="14"/>
-      <c r="W42" s="34" t="s">
+      <c r="J42" s="17"/>
+      <c r="V42" s="15"/>
+      <c r="W42" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="X42" s="33" t="s">
+      <c r="X42" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="Y42" s="35" t="s">
+      <c r="Y42" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="Z42" s="33" t="s">
+      <c r="Z42" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AA42" s="22"/>
-      <c r="AB42" s="33" t="s">
+      <c r="AA42" s="23" t="str">
+        <f aca="false">"("&amp; TEXT(SLOPE(I41:I46,G41:G46), "0.000") &amp; ") (" &amp; TEXT(E16*2, "0.000") &amp; "x10^-3 m)"</f>
+        <v>(72428.571) (0.047x10^-3 m)</v>
+      </c>
+      <c r="AB42" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AC42" s="36"/>
-      <c r="AD42" s="16"/>
+      <c r="AC42" s="37" t="n">
+        <f aca="false">E16 * 2 / 1000 * SLOPE(I41:I46,G41:G46)/(8.8541*E9)</f>
+        <v>3.78077841407511</v>
+      </c>
+      <c r="AD42" s="17"/>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D43" s="14"/>
-      <c r="E43" s="18" t="n">
-        <f aca="false">$E$8+G43</f>
+      <c r="D43" s="15"/>
+      <c r="E43" s="19" t="n">
+        <f aca="false">2*$E$8-G43</f>
         <v>0.295</v>
       </c>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18" t="n">
-        <f aca="false">G42+0.01</f>
-        <v>0.04</v>
-      </c>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19" t="n">
+      <c r="F43" s="19"/>
+      <c r="G43" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G43) - 41) + 2)/100)</f>
+        <v>0.215</v>
+      </c>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20" t="n">
         <f aca="false">5.15*1000</f>
         <v>5150</v>
       </c>
-      <c r="J43" s="16"/>
-      <c r="V43" s="14"/>
-      <c r="W43" s="34"/>
-      <c r="X43" s="33"/>
-      <c r="Y43" s="37" t="s">
+      <c r="J43" s="17"/>
+      <c r="V43" s="15"/>
+      <c r="W43" s="35"/>
+      <c r="X43" s="34"/>
+      <c r="Y43" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="Z43" s="33"/>
-      <c r="AA43" s="19"/>
-      <c r="AB43" s="33"/>
-      <c r="AC43" s="36"/>
-      <c r="AD43" s="16"/>
+      <c r="Z43" s="34"/>
+      <c r="AA43" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB43" s="34"/>
+      <c r="AC43" s="37"/>
+      <c r="AD43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D44" s="14"/>
-      <c r="E44" s="18" t="n">
-        <f aca="false">$E$8+G44</f>
+      <c r="D44" s="15"/>
+      <c r="E44" s="19" t="n">
+        <f aca="false">2*$E$8-G44</f>
         <v>0.305</v>
       </c>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18" t="n">
-        <f aca="false">G43+0.01</f>
-        <v>0.05</v>
-      </c>
-      <c r="H44" s="19"/>
-      <c r="I44" s="0" t="n">
+      <c r="F44" s="19"/>
+      <c r="G44" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G44) - 41) + 2)/100)</f>
+        <v>0.205</v>
+      </c>
+      <c r="H44" s="20"/>
+      <c r="I44" s="1" t="n">
         <f aca="false">4.3*1000</f>
         <v>4300</v>
       </c>
-      <c r="J44" s="16"/>
-      <c r="V44" s="20"/>
-      <c r="W44" s="22"/>
-      <c r="X44" s="22"/>
-      <c r="Y44" s="22"/>
-      <c r="Z44" s="22"/>
-      <c r="AA44" s="22"/>
-      <c r="AB44" s="22"/>
-      <c r="AC44" s="22"/>
-      <c r="AD44" s="23"/>
+      <c r="J44" s="17"/>
+      <c r="V44" s="21"/>
+      <c r="W44" s="23"/>
+      <c r="X44" s="23"/>
+      <c r="Y44" s="23"/>
+      <c r="Z44" s="23"/>
+      <c r="AA44" s="23"/>
+      <c r="AB44" s="23"/>
+      <c r="AC44" s="23"/>
+      <c r="AD44" s="24"/>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D45" s="14"/>
-      <c r="E45" s="18" t="n">
-        <f aca="false">$E$8+G45</f>
+      <c r="D45" s="15"/>
+      <c r="E45" s="19" t="n">
+        <f aca="false">2*$E$8-G45</f>
         <v>0.315</v>
       </c>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18" t="n">
-        <f aca="false">G44+0.01</f>
-        <v>0.06</v>
-      </c>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19" t="n">
+      <c r="F45" s="19"/>
+      <c r="G45" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G45) - 41) + 2)/100)</f>
+        <v>0.195</v>
+      </c>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20" t="n">
         <f aca="false">3.6*1000</f>
         <v>3600</v>
       </c>
-      <c r="J45" s="16"/>
-      <c r="V45" s="19"/>
-      <c r="W45" s="38"/>
-      <c r="X45" s="38"/>
-      <c r="Y45" s="38"/>
-      <c r="Z45" s="38"/>
-      <c r="AA45" s="38"/>
-      <c r="AB45" s="38"/>
-      <c r="AC45" s="19"/>
-      <c r="AD45" s="19"/>
+      <c r="J45" s="17"/>
+      <c r="V45" s="20"/>
+      <c r="W45" s="39"/>
+      <c r="X45" s="39"/>
+      <c r="Y45" s="39"/>
+      <c r="Z45" s="39"/>
+      <c r="AA45" s="39"/>
+      <c r="AB45" s="39"/>
+      <c r="AC45" s="20"/>
+      <c r="AD45" s="20"/>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D46" s="14"/>
-      <c r="E46" s="18" t="n">
-        <f aca="false">$E$8+G46</f>
+      <c r="D46" s="15"/>
+      <c r="E46" s="19" t="n">
+        <f aca="false">2*$E$8-G46</f>
         <v>0.325</v>
       </c>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18" t="n">
-        <f aca="false">G45+0.01</f>
-        <v>0.07</v>
-      </c>
-      <c r="H46" s="19"/>
-      <c r="I46" s="0" t="n">
+      <c r="F46" s="19"/>
+      <c r="G46" s="19" t="n">
+        <f aca="false">($E$8-((ROW(G46) - 41) + 2)/100)</f>
+        <v>0.185</v>
+      </c>
+      <c r="H46" s="20"/>
+      <c r="I46" s="1" t="n">
         <f aca="false">2.7*1000</f>
         <v>2700</v>
       </c>
-      <c r="J46" s="16"/>
-      <c r="V46" s="19"/>
-      <c r="W46" s="39"/>
-      <c r="X46" s="39"/>
-      <c r="Y46" s="39"/>
-      <c r="Z46" s="39"/>
-      <c r="AA46" s="18"/>
-      <c r="AB46" s="18"/>
-      <c r="AC46" s="32"/>
-      <c r="AD46" s="19"/>
+      <c r="J46" s="17"/>
+      <c r="V46" s="20"/>
+      <c r="W46" s="40"/>
+      <c r="X46" s="40"/>
+      <c r="Y46" s="40"/>
+      <c r="Z46" s="40"/>
+      <c r="AA46" s="19"/>
+      <c r="AB46" s="19"/>
+      <c r="AC46" s="33"/>
+      <c r="AD46" s="20"/>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D47" s="14"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="16"/>
-      <c r="V47" s="19"/>
-      <c r="W47" s="19"/>
-      <c r="X47" s="19"/>
-      <c r="Y47" s="19"/>
-      <c r="Z47" s="19"/>
-      <c r="AA47" s="19"/>
-      <c r="AB47" s="19"/>
-      <c r="AC47" s="19"/>
-      <c r="AD47" s="19"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="17"/>
+      <c r="V47" s="20"/>
+      <c r="W47" s="20"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
+      <c r="Z47" s="20"/>
+      <c r="AA47" s="20"/>
+      <c r="AB47" s="20"/>
+      <c r="AC47" s="20"/>
+      <c r="AD47" s="20"/>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D48" s="14"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="16"/>
-      <c r="V48" s="19"/>
-      <c r="W48" s="38"/>
-      <c r="X48" s="19"/>
-      <c r="Y48" s="19"/>
-      <c r="Z48" s="19"/>
-      <c r="AA48" s="19"/>
-      <c r="AB48" s="19"/>
-      <c r="AC48" s="19"/>
-      <c r="AD48" s="19"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="17"/>
+      <c r="V48" s="20"/>
+      <c r="W48" s="39"/>
+      <c r="X48" s="20"/>
+      <c r="Y48" s="20"/>
+      <c r="Z48" s="20"/>
+      <c r="AA48" s="20"/>
+      <c r="AB48" s="20"/>
+      <c r="AC48" s="20"/>
+      <c r="AD48" s="20"/>
     </row>
     <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D49" s="14"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="16"/>
-      <c r="V49" s="19"/>
-      <c r="W49" s="19"/>
-      <c r="X49" s="19"/>
-      <c r="Y49" s="19"/>
-      <c r="Z49" s="19"/>
-      <c r="AA49" s="19"/>
-      <c r="AB49" s="19"/>
-      <c r="AC49" s="19"/>
-      <c r="AD49" s="19"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="17"/>
+      <c r="V49" s="20"/>
+      <c r="W49" s="20"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
+      <c r="Z49" s="20"/>
+      <c r="AA49" s="20"/>
+      <c r="AB49" s="20"/>
+      <c r="AC49" s="20"/>
+      <c r="AD49" s="20"/>
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D50" s="14"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="16"/>
-      <c r="V50" s="19"/>
-      <c r="W50" s="40"/>
-      <c r="X50" s="41"/>
-      <c r="Y50" s="33"/>
-      <c r="Z50" s="18"/>
-      <c r="AA50" s="18"/>
-      <c r="AB50" s="19"/>
-      <c r="AC50" s="19"/>
-      <c r="AD50" s="19"/>
-    </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D51" s="20"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="22"/>
-      <c r="I51" s="22"/>
-      <c r="J51" s="23"/>
-      <c r="V51" s="19"/>
-      <c r="W51" s="19"/>
-      <c r="X51" s="19"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="19"/>
-      <c r="AA51" s="19"/>
-      <c r="AB51" s="19"/>
-      <c r="AC51" s="19"/>
-      <c r="AD51" s="19"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="17"/>
+      <c r="V50" s="20"/>
+      <c r="W50" s="41"/>
+      <c r="X50" s="42"/>
+      <c r="Y50" s="34"/>
+      <c r="Z50" s="19"/>
+      <c r="AA50" s="19"/>
+      <c r="AB50" s="20"/>
+      <c r="AC50" s="20"/>
+      <c r="AD50" s="20"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D51" s="21"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="23"/>
+      <c r="I51" s="23"/>
+      <c r="J51" s="24"/>
+      <c r="V51" s="20"/>
+      <c r="W51" s="20"/>
+      <c r="X51" s="20"/>
+      <c r="Y51" s="20"/>
+      <c r="Z51" s="20"/>
+      <c r="AA51" s="20"/>
+      <c r="AB51" s="20"/>
+      <c r="AC51" s="20"/>
+      <c r="AD51" s="20"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E52" s="42"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="1"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="2"/>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
